--- a/data/trans_orig/barthel-Edad-trans_orig.xlsx
+++ b/data/trans_orig/barthel-Edad-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de dependencia funcional para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Puntuación media de la escala de dependencia funcional para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -648,62 +648,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98,77</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97,31</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98,4</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98,24</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97,86</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97,56</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98,36</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98,28</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96,95</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97,96</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98,31</t>
         </is>
       </c>
     </row>
@@ -716,69 +716,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97,53; 99,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95,63; 98,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97,52; 99,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97,41; 98,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96,59; 98,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95,21; 97,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96,38; 98,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97,36; 99,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97,57; 98,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96,0; 97,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97,25; 98,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97,67; 99,12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -788,62 +788,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95,54</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92,31</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93,3</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93,77</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93,18</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86,64</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89,87</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87,39</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94,09</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88,86</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91,22</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89,94</t>
         </is>
       </c>
     </row>
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,68; 96,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89,06; 94,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91,19; 94,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>92,18; 94,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91,05; 94,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,1; 88,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,27; 91,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,92; 88,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>92,74; 95,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,97; 90,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89,62; 92,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,94; 90,84</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -928,62 +928,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97,42</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95,08</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96,19</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96,31</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95,55</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93,61</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93,85</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96,35</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92,98</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94,72</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94,8</t>
         </is>
       </c>
     </row>
@@ -996,786 +996,81 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96,43; 98,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,78; 96,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95,22; 97,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95,55; 96,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>94,39; 96,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89,75; 92,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>92,21; 94,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>92,04; 96,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95,54; 96,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91,85; 93,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,88; 95,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,89; 96,64</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>98,77</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>97,31</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>98,4</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>98,24</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,86</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,64</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,56</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>98,36</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98,28</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>96,95</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>97,96</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>97,58; 99,37</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>95,74; 98,34</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>97,44; 99,07</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>97,48; 98,7</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>96,78; 98,62</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>95,35; 97,66</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>96,49; 98,28</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>97,32; 99,41</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>97,52; 98,82</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>95,99; 97,81</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>97,32; 98,45</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>97,72; 99,16</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>95,54</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>92,31</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>93,3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>93,77</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>93,18</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86,64</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>89,87</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>87,39</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>94,09</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>88,86</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>91,22</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>89,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>93,53; 96,86</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>89,13; 94,53</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>91,39; 95,0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>92,34; 94,96</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>91,03; 94,87</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,95; 88,61</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,28; 91,7</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>85,88; 88,6</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>92,57; 95,28</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>86,84; 90,36</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>89,74; 92,6</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>88,83; 90,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>97,42</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>95,08</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>96,19</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>96,31</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>95,55</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>91,4</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>93,61</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>93,85</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>96,35</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>92,98</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>94,72</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>94,8</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>96,28; 98,04</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>93,51; 96,26</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>95,12; 97,0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>95,61; 96,91</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>94,41; 96,51</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>89,78; 92,64</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>92,27; 94,69</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>92,05; 96,47</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>95,6; 96,98</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>91,91; 93,85</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>93,8; 95,39</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>93,93; 96,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/barthel-Edad-trans_orig.xlsx
+++ b/data/trans_orig/barthel-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98,24</t>
+          <t>98,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>98,36</t>
+          <t>97,45</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>98,31</t>
+          <t>97,87</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>97,53; 99,38</t>
+          <t>97,67; 99,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95,63; 98,28</t>
+          <t>95,77; 98,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,52; 99,04</t>
+          <t>97,4; 99,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97,41; 98,73</t>
+          <t>97,69; 98,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,59; 98,62</t>
+          <t>96,63; 98,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,21; 97,62</t>
+          <t>95,23; 97,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,38; 98,22</t>
+          <t>96,61; 98,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>97,36; 99,39</t>
+          <t>96,7; 97,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>97,57; 98,87</t>
+          <t>97,48; 98,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96,0; 97,66</t>
+          <t>96,01; 97,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97,25; 98,43</t>
+          <t>97,25; 98,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,67; 99,12</t>
+          <t>97,4; 98,25</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93,77</t>
+          <t>93,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87,39</t>
+          <t>87,45</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,94</t>
+          <t>90,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,68; 96,93</t>
+          <t>93,52; 96,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,06; 94,48</t>
+          <t>89,57; 94,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,19; 94,79</t>
+          <t>91,22; 94,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,18; 94,88</t>
+          <t>92,49; 95,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,05; 94,79</t>
+          <t>91,07; 94,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,1; 88,7</t>
+          <t>83,91; 88,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,27; 91,67</t>
+          <t>87,43; 91,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,92; 88,75</t>
+          <t>85,88; 88,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>92,74; 95,28</t>
+          <t>92,58; 95,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86,97; 90,46</t>
+          <t>86,89; 90,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89,62; 92,55</t>
+          <t>89,74; 92,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,94; 90,84</t>
+          <t>89,07; 90,95</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96,31</t>
+          <t>96,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93,85</t>
+          <t>92,31</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,8</t>
+          <t>94,13</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>96,43; 98,09</t>
+          <t>96,54; 98,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93,78; 96,3</t>
+          <t>93,51; 96,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95,22; 97,02</t>
+          <t>95,15; 96,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95,55; 96,93</t>
+          <t>95,72; 96,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,39; 96,43</t>
+          <t>94,3; 96,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,75; 92,58</t>
+          <t>89,94; 92,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,21; 94,73</t>
+          <t>92,25; 94,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,04; 96,69</t>
+          <t>91,45; 93,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95,54; 96,95</t>
+          <t>95,63; 96,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,85; 93,82</t>
+          <t>92,0; 93,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93,88; 95,48</t>
+          <t>93,97; 95,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93,89; 96,64</t>
+          <t>93,55; 94,65</t>
         </is>
       </c>
     </row>
